--- a/data/cci/cci-sensor.xlsx
+++ b/data/cci/cci-sensor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{26BBE7DF-4C63-4A86-92DF-2DFFF951F08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9818955-6961-4C12-952A-B8D495986EC7}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{26BBE7DF-4C63-4A86-92DF-2DFFF951F08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C59D353-B00D-479B-B3EA-622C9CE63562}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AC6267AA-9592-A246-9899-93CEA800D98F}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="34515" windowHeight="15285" xr2:uid="{AC6267AA-9592-A246-9899-93CEA800D98F}"/>
   </bookViews>
   <sheets>
     <sheet name="cci-sensor" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="418">
   <si>
     <t>URI</t>
   </si>
@@ -1264,6 +1264,18 @@
   </si>
   <si>
     <t>https://space.oscar.wmo.int/instruments/view/mopitt</t>
+  </si>
+  <si>
+    <t>sen_ahi</t>
+  </si>
+  <si>
+    <t>AHI</t>
+  </si>
+  <si>
+    <t>Advanced Himawari Imager</t>
+  </si>
+  <si>
+    <t>https://space.oscar.wmo.int/instruments/view/ahi</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1513,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1523,6 +1535,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="19"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent" xfId="7" xr:uid="{7985A975-9802-3248-9910-E2AB4182EA1B}"/>
@@ -2912,7 +2925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE65322-9E0A-7A45-9C36-668BB13B834C}">
-  <dimension ref="A1:BL102"/>
+  <dimension ref="A1:BL103"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60.7109375" customWidth="1"/>
@@ -4444,16 +4457,31 @@
         <v>413</v>
       </c>
     </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>414</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{57D44E5B-F05F-4247-A1E8-17B16E6BFB2A}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{341302AD-3E4C-4045-8899-137E8885875F}"/>
     <hyperlink ref="E93" r:id="rId3" xr:uid="{39683A05-519C-EE4D-B2B3-2BDF91E32A97}"/>
+    <hyperlink ref="E103" r:id="rId4" xr:uid="{BBF6D401-DBB6-4301-820D-1D1954868F92}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/cci/cci-sensor.xlsx
+++ b/data/cci/cci-sensor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{26BBE7DF-4C63-4A86-92DF-2DFFF951F08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C59D353-B00D-479B-B3EA-622C9CE63562}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{26BBE7DF-4C63-4A86-92DF-2DFFF951F08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C32BE0-CB86-4E08-B1F4-9E11164180FD}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="34515" windowHeight="15285" xr2:uid="{AC6267AA-9592-A246-9899-93CEA800D98F}"/>
+    <workbookView xWindow="39105" yWindow="2940" windowWidth="34515" windowHeight="15285" xr2:uid="{AC6267AA-9592-A246-9899-93CEA800D98F}"/>
   </bookViews>
   <sheets>
     <sheet name="cci-sensor" sheetId="1" r:id="rId1"/>
@@ -1266,9 +1266,6 @@
     <t>https://space.oscar.wmo.int/instruments/view/mopitt</t>
   </si>
   <si>
-    <t>sen_ahi</t>
-  </si>
-  <si>
     <t>AHI</t>
   </si>
   <si>
@@ -1276,6 +1273,9 @@
   </si>
   <si>
     <t>https://space.oscar.wmo.int/instruments/view/ahi</t>
+  </si>
+  <si>
+    <t>sens_ahi</t>
   </si>
 </sst>
 </file>
@@ -4459,16 +4459,16 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
+        <v>417</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="E103" s="9" t="s">
         <v>416</v>
-      </c>
-      <c r="E103" s="9" t="s">
-        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/data/cci/cci-sensor.xlsx
+++ b/data/cci/cci-sensor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{26BBE7DF-4C63-4A86-92DF-2DFFF951F08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C32BE0-CB86-4E08-B1F4-9E11164180FD}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{26BBE7DF-4C63-4A86-92DF-2DFFF951F08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{604A036B-93E2-4326-8935-41DC17BEEE90}"/>
   <bookViews>
-    <workbookView xWindow="39105" yWindow="2940" windowWidth="34515" windowHeight="15285" xr2:uid="{AC6267AA-9592-A246-9899-93CEA800D98F}"/>
+    <workbookView xWindow="38280" yWindow="-60" windowWidth="38640" windowHeight="21120" xr2:uid="{AC6267AA-9592-A246-9899-93CEA800D98F}"/>
   </bookViews>
   <sheets>
     <sheet name="cci-sensor" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="419">
   <si>
     <t>URI</t>
   </si>
@@ -1276,6 +1276,9 @@
   </si>
   <si>
     <t>sens_ahi</t>
+  </si>
+  <si>
+    <t>SAR-C</t>
   </si>
 </sst>
 </file>
@@ -3973,6 +3976,9 @@
       <c r="B69" s="3" t="s">
         <v>278</v>
       </c>
+      <c r="C69" s="3" t="s">
+        <v>418</v>
+      </c>
       <c r="D69" s="3" t="s">
         <v>279</v>
       </c>
